--- a/DateBase/orders/Nhat 48_2026-8-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-8-5.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="41">
       <c r="C41" t="str">
-        <v>619_康乃馨樱桃紫_undefined_undefined_20stems</v>
+        <v>901_康乃馨新娘_undefined_undefined_1bunch</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-8-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-8-5.xlsx
@@ -793,6 +793,9 @@
       <c r="C41" t="str">
         <v>901_康乃馨新娘_undefined_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -851,7 +854,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0103515264010251030506253515271855551055540710301652610253252850220</v>
+        <v>0103515264010251030506253515271855551055540710301652610253252850221</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-8-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-8-5.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -794,12 +794,45 @@
         <v>901_康乃馨新娘_undefined_undefined_1bunch</v>
       </c>
       <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
         <v>1</v>
+      </c>
+      <c r="C42" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2</v>
+      </c>
+      <c r="C43" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>3</v>
+      </c>
+      <c r="C44" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L44"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -854,7 +887,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0103515264010251030506253515271855551055540710301652610253252850221</v>
+        <v>01035152640102510305062535152718555510555407103016526102532528502210101010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-8-5.xlsx
+++ b/DateBase/orders/Nhat 48_2026-8-5.xlsx
@@ -889,6 +889,9 @@
       <c r="G2" t="str">
         <v>01035152640102510305062535152718555510555407103016526102532528502210101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
